--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.69143546143587</v>
+        <v>3.524858262483329</v>
       </c>
       <c r="D2" t="n">
-        <v>17.08436542609601</v>
+        <v>2.776209381740601</v>
       </c>
       <c r="E2" t="n">
-        <v>6.007089567479378</v>
+        <v>0.9761520547153989</v>
       </c>
       <c r="F2" t="n">
-        <v>12.79358216797524</v>
+        <v>2.078957102295977</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.1049731745428</v>
+        <v>3.104558140863205</v>
       </c>
       <c r="D3" t="n">
-        <v>36.85180532288148</v>
+        <v>5.98841836496824</v>
       </c>
       <c r="E3" t="n">
-        <v>6.007089567479378</v>
+        <v>0.9761520547153989</v>
       </c>
       <c r="F3" t="n">
-        <v>12.79358216797524</v>
+        <v>2.078957102295977</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.41408953534421</v>
+        <v>2.017289549493435</v>
       </c>
       <c r="D4" t="n">
-        <v>5.166921161894013</v>
+        <v>0.8396246888077772</v>
       </c>
       <c r="E4" t="n">
-        <v>6.007089567479378</v>
+        <v>0.9761520547153989</v>
       </c>
       <c r="F4" t="n">
-        <v>12.79358216797524</v>
+        <v>2.078957102295977</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.276860988431024</v>
+        <v>1.019989910620041</v>
       </c>
       <c r="D5" t="n">
-        <v>5.918595855988408</v>
+        <v>0.9617718265981163</v>
       </c>
       <c r="E5" t="n">
-        <v>6.007089567479378</v>
+        <v>0.9761520547153989</v>
       </c>
       <c r="F5" t="n">
-        <v>12.79358216797524</v>
+        <v>2.078957102295977</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
